--- a/quizzes/001_retail_onboarding_quiz--quizzes.xlsx
+++ b/quizzes/001_retail_onboarding_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz</t>
+          <t>Retail Onboarding Quiz</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>Sales Knowledge</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>Marketing and Branding</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>branding</t>
+          <t>Onboarding Process</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz_part2</t>
+          <t>Retail Environment</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>Team Collaboration and Communication</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz_part3</t>
+          <t>Onboarding Review and Feedback</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz_part4</t>
+          <t>Retail Team Performance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>Employee Onboarding Process</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>branding</t>
+          <t>Team Performance Evaluation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz_part5</t>
+          <t>Retail Knowledge</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz_part6</t>
+          <t>Retail Onboarding Quiz End</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz_part7</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz_part8</t>
+          <t>More information on retail onboarding</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz_part9</t>
+          <t>Page 15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz_part10</t>
+          <t>Page 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz_part11</t>
+          <t>Page 17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,172 +916,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>retail_onboarding_quiz_part12</t>
+          <t>Page 18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>retail_onboarding_quiz_part13</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>retail_onboarding_quiz_part14</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>retail_onboarding_quiz_part15</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>retail_onboarding_quiz_part16</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>retail_onboarding_quiz_part17</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>retail_onboarding_quiz_part18</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>retail_onboarding_quiz_part19</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>upselling_vs._cross-selling</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Upselling vs. Cross-Selling</t>
         </is>
       </c>
     </row>
@@ -1148,29 +987,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>handling_customer_complaints</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Handling Customer Complaints</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>building_customer_relationships</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Building Customer Relationships</t>
         </is>
       </c>
     </row>
@@ -1182,46 +1021,454 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>brand_storytelling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Brand Storytelling</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>social_media_in_retail_branding</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Social Media in Retail Branding</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>page_3_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>visual_identity</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Visual Identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>page_4_choices</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>new_employee_onboarding</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>New Employee Onboarding</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>page_4_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>feedback_and_performance_evaluation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Feedback and Performance Evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>page_4_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>goals_and_objectives</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Goals and Objectives</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>page_5_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>store_layout_and_design</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Store Layout and Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>page_5_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>merchandising_and_display</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Merchandising and Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>page_5_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>visual_merchandising</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Visual Merchandising</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>collaboration_strategies</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Collaboration Strategies</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>communication_tactics</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Communication Tactics</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>page_6_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>feedback_and_coaching</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Feedback and Coaching</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>feedback_types</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Feedback Types</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>performance_impact</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Performance Impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>page_7_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>development_goals</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Development Goals</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sales_goals</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sales Goals</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>collaboration_strategies</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Collaboration Strategies</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>communication_tactics</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Communication Tactics</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>page_9_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>onboarding_process_steps</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Onboarding Process Steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>page_9_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>new_employee_onboarding</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New Employee Onboarding</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>page_9_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>feedback_and_performance_evaluation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Feedback and Performance Evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>page_10_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>performance_metrics</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Performance Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>page_10_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>collaboration_strategies</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Collaboration Strategies</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>page_10_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>communication_tactics</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Communication Tactics</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>page_11_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>what_is_retail?</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>What is retail?</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>page_11_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>retail_vs._online_shopping</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Retail vs. Online Shopping</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>page_11_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>main_goal_of_retail_store</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Main goal of retail store</t>
         </is>
       </c>
     </row>
